--- a/output/20260630_fix_owner_new_import/active_problem_3_non_named_payment_left_179_cases_20260630.xlsx
+++ b/output/20260630_fix_owner_new_import/active_problem_3_non_named_payment_left_179_cases_20260630.xlsx
@@ -632,7 +632,7 @@
       </c>
       <c r="T2" s="2" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Петрова Полина Владимировна</t>
         </is>
       </c>
     </row>
@@ -6750,7 +6750,7 @@
       </c>
       <c r="T84" s="2" t="inlineStr">
         <is>
-          <t>УТОЧНИТЬ: Карельский</t>
+          <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
     </row>

--- a/output/20260630_fix_owner_new_import/active_problem_3_non_named_payment_left_179_cases_20260630.xlsx
+++ b/output/20260630_fix_owner_new_import/active_problem_3_non_named_payment_left_179_cases_20260630.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Импорт_абонементы" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Импорт_абонементы'!$A$1:$U$180</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Импорт_абонементы'!$A$1:$V$180</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:U180"/>
+  <dimension ref="A1:V180"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="10" customWidth="1" min="1" max="1"/>
@@ -459,6 +459,7 @@
     <col width="14" customWidth="1" min="19" max="19"/>
     <col width="17" customWidth="1" min="20" max="20"/>
     <col width="35" customWidth="1" min="21" max="21"/>
+    <col width="31" customWidth="1" min="22" max="22"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -565,6 +566,11 @@
       <c r="U1" s="1" t="inlineStr">
         <is>
           <t>manager</t>
+        </is>
+      </c>
+      <c r="V1" s="1" t="inlineStr">
+        <is>
+          <t>филиал</t>
         </is>
       </c>
     </row>
@@ -642,6 +648,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="V2" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="n"/>
@@ -717,6 +728,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="V3" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="n"/>
@@ -792,6 +808,11 @@
       <c r="U4" s="2" t="inlineStr">
         <is>
           <t>Абраамян Татьяна Викторовна</t>
+        </is>
+      </c>
+      <c r="V4" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
         </is>
       </c>
     </row>
@@ -869,6 +890,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="V5" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="n"/>
@@ -944,6 +970,11 @@
       <c r="U6" s="2" t="inlineStr">
         <is>
           <t>Пеуна Анастасия Ивановна</t>
+        </is>
+      </c>
+      <c r="V6" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
         </is>
       </c>
     </row>
@@ -1021,6 +1052,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="V7" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="n"/>
@@ -1096,6 +1132,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="V8" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" s="2" t="n"/>
@@ -1171,6 +1212,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="V9" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="2" t="n"/>
@@ -1246,6 +1292,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="V10" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" s="2" t="n"/>
@@ -1321,6 +1372,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="V11" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" s="2" t="n"/>
@@ -1398,6 +1454,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="V12" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="2" t="n"/>
@@ -1475,6 +1536,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="V13" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" s="2" t="n"/>
@@ -1552,6 +1618,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="V14" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" s="2" t="n"/>
@@ -1627,6 +1698,11 @@
       <c r="U15" s="2" t="inlineStr">
         <is>
           <t>Пеуна Анастасия Ивановна</t>
+        </is>
+      </c>
+      <c r="V15" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
         </is>
       </c>
     </row>
@@ -1704,6 +1780,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="V16" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" s="2" t="n"/>
@@ -1779,6 +1860,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="V17" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" s="2" t="n"/>
@@ -1854,6 +1940,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="V18" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" s="2" t="n"/>
@@ -1931,6 +2022,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="V19" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" s="2" t="n"/>
@@ -2008,6 +2104,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="V20" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" s="2" t="n"/>
@@ -2085,6 +2186,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="V21" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" s="2" t="n"/>
@@ -2162,6 +2268,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="V22" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" s="2" t="n"/>
@@ -2237,6 +2348,11 @@
       <c r="U23" s="2" t="inlineStr">
         <is>
           <t>Пилия Анастасия Артуровна</t>
+        </is>
+      </c>
+      <c r="V23" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
         </is>
       </c>
     </row>
@@ -2314,6 +2430,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="V24" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" s="2" t="n"/>
@@ -2389,6 +2510,11 @@
       <c r="U25" s="2" t="inlineStr">
         <is>
           <t>Пилия Анастасия Артуровна</t>
+        </is>
+      </c>
+      <c r="V25" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
         </is>
       </c>
     </row>
@@ -2466,6 +2592,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="V26" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" s="2" t="n"/>
@@ -2541,6 +2672,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="V27" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" s="2" t="n"/>
@@ -2616,6 +2752,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="V28" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" s="2" t="n"/>
@@ -2691,6 +2832,11 @@
       <c r="U29" s="2" t="inlineStr">
         <is>
           <t>Седунова Анна Сергеевна</t>
+        </is>
+      </c>
+      <c r="V29" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
         </is>
       </c>
     </row>
@@ -2768,6 +2914,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="V30" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" s="2" t="n"/>
@@ -2843,6 +2994,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="V31" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" s="2" t="n"/>
@@ -2918,6 +3074,11 @@
       <c r="U32" s="2" t="inlineStr">
         <is>
           <t>Фёдорова Милана Андреевна</t>
+        </is>
+      </c>
+      <c r="V32" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
         </is>
       </c>
     </row>
@@ -2995,6 +3156,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="V33" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" s="2" t="n"/>
@@ -3070,6 +3236,11 @@
       <c r="U34" s="2" t="inlineStr">
         <is>
           <t>Соколова Анастасия Александровна</t>
+        </is>
+      </c>
+      <c r="V34" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
         </is>
       </c>
     </row>
@@ -3147,6 +3318,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="V35" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" s="2" t="n"/>
@@ -3222,6 +3398,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="V36" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" s="2" t="n"/>
@@ -3297,6 +3478,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="V37" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" s="2" t="n"/>
@@ -3372,6 +3558,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="V38" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" s="2" t="n"/>
@@ -3447,6 +3638,11 @@
       <c r="U39" s="2" t="inlineStr">
         <is>
           <t>Пеуна Анастасия Ивановна</t>
+        </is>
+      </c>
+      <c r="V39" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
         </is>
       </c>
     </row>
@@ -3524,6 +3720,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="V40" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" s="2" t="n"/>
@@ -3599,6 +3800,11 @@
       <c r="U41" s="2" t="inlineStr">
         <is>
           <t>Васильева Яна Денисовна</t>
+        </is>
+      </c>
+      <c r="V41" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
         </is>
       </c>
     </row>
@@ -3676,6 +3882,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="V42" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" s="2" t="n"/>
@@ -3751,6 +3962,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="V43" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" s="2" t="n"/>
@@ -3826,6 +4042,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="V44" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" s="2" t="n"/>
@@ -3901,6 +4122,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="V45" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" s="2" t="n"/>
@@ -3976,6 +4202,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="V46" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" s="2" t="n"/>
@@ -4051,6 +4282,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="V47" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" s="2" t="n"/>
@@ -4126,6 +4362,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="V48" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" s="2" t="n"/>
@@ -4201,6 +4442,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="V49" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" s="2" t="n"/>
@@ -4276,6 +4522,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="V50" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" s="2" t="n"/>
@@ -4351,6 +4602,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="V51" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" s="2" t="n"/>
@@ -4426,6 +4682,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="V52" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" s="2" t="n"/>
@@ -4501,6 +4762,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="V53" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" s="2" t="n"/>
@@ -4576,6 +4842,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="V54" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" s="2" t="n"/>
@@ -4651,6 +4922,11 @@
       <c r="U55" s="2" t="inlineStr">
         <is>
           <t>Лисовская Екатерина Александровна</t>
+        </is>
+      </c>
+      <c r="V55" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
         </is>
       </c>
     </row>
@@ -4728,6 +5004,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="V56" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" s="2" t="n"/>
@@ -4803,6 +5084,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="V57" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" s="2" t="n"/>
@@ -4878,6 +5164,11 @@
       <c r="U58" s="2" t="inlineStr">
         <is>
           <t>Петрова Полина Владимировна</t>
+        </is>
+      </c>
+      <c r="V58" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
         </is>
       </c>
     </row>
@@ -4955,6 +5246,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="V59" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" s="2" t="n"/>
@@ -5030,6 +5326,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="V60" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" s="2" t="n"/>
@@ -5105,6 +5406,11 @@
       <c r="U61" s="2" t="inlineStr">
         <is>
           <t>Пеуна Анастасия Ивановна</t>
+        </is>
+      </c>
+      <c r="V61" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
         </is>
       </c>
     </row>
@@ -5182,6 +5488,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="V62" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" s="2" t="n"/>
@@ -5257,6 +5568,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="V63" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" s="2" t="n"/>
@@ -5334,6 +5650,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="V64" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" s="2" t="n"/>
@@ -5409,6 +5730,11 @@
       <c r="U65" s="2" t="inlineStr">
         <is>
           <t>Анухина Кристина Алексеевна</t>
+        </is>
+      </c>
+      <c r="V65" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
         </is>
       </c>
     </row>
@@ -5486,6 +5812,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="V66" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" s="2" t="n"/>
@@ -5561,6 +5892,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="V67" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" s="2" t="n"/>
@@ -5636,6 +5972,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="V68" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" s="2" t="n"/>
@@ -5711,6 +6052,11 @@
       <c r="U69" s="2" t="inlineStr">
         <is>
           <t>Яковлева Александра Владимировна</t>
+        </is>
+      </c>
+      <c r="V69" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
         </is>
       </c>
     </row>
@@ -5788,6 +6134,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="V70" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" s="2" t="n"/>
@@ -5863,6 +6214,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="V71" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" s="2" t="n"/>
@@ -5938,6 +6294,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="V72" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" s="2" t="n"/>
@@ -6013,6 +6374,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="V73" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" s="2" t="n"/>
@@ -6088,6 +6454,11 @@
           <t>Седунова Анна Сергеевна</t>
         </is>
       </c>
+      <c r="V74" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" s="2" t="n"/>
@@ -6165,6 +6536,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="V75" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" s="2" t="n"/>
@@ -6240,6 +6616,11 @@
       <c r="U76" s="2" t="inlineStr">
         <is>
           <t>Яковлева Александра Владимировна</t>
+        </is>
+      </c>
+      <c r="V76" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
         </is>
       </c>
     </row>
@@ -6317,6 +6698,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="V77" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" s="2" t="n"/>
@@ -6392,6 +6778,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="V78" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" s="2" t="n"/>
@@ -6467,6 +6858,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="V79" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" s="2" t="n"/>
@@ -6542,6 +6938,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="V80" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" s="2" t="n"/>
@@ -6617,6 +7018,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="V81" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" s="2" t="n"/>
@@ -6692,6 +7098,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="V82" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" s="2" t="n"/>
@@ -6767,6 +7178,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="V83" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" s="2" t="n"/>
@@ -6842,6 +7258,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="V84" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" s="2" t="n"/>
@@ -6917,6 +7338,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="V85" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" s="2" t="n"/>
@@ -6992,6 +7418,11 @@
       <c r="U86" s="2" t="inlineStr">
         <is>
           <t>Яковлева Александра Владимировна</t>
+        </is>
+      </c>
+      <c r="V86" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
         </is>
       </c>
     </row>
@@ -7069,6 +7500,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="V87" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" s="2" t="n"/>
@@ -7144,6 +7580,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="V88" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" s="2" t="n"/>
@@ -7219,6 +7660,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="V89" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" s="2" t="n"/>
@@ -7290,6 +7736,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="V90" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" s="2" t="n"/>
@@ -7365,6 +7816,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="V91" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" s="2" t="n"/>
@@ -7440,6 +7896,11 @@
       <c r="U92" s="2" t="inlineStr">
         <is>
           <t>Абраамян Татьяна Викторовна</t>
+        </is>
+      </c>
+      <c r="V92" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
         </is>
       </c>
     </row>
@@ -7517,6 +7978,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="V93" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" s="2" t="n"/>
@@ -7588,6 +8054,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="V94" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" s="2" t="n"/>
@@ -7663,6 +8134,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="V95" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" s="2" t="n"/>
@@ -7738,6 +8214,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="V96" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" s="2" t="n"/>
@@ -7813,6 +8294,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="V97" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" s="2" t="n"/>
@@ -7888,6 +8374,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="V98" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" s="2" t="n"/>
@@ -7963,6 +8454,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="V99" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" s="2" t="n"/>
@@ -8040,6 +8536,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="V100" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" s="2" t="n"/>
@@ -8117,6 +8618,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="V101" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" s="2" t="n"/>
@@ -8192,6 +8698,11 @@
       <c r="U102" s="2" t="inlineStr">
         <is>
           <t>Лисовская Екатерина Александровна</t>
+        </is>
+      </c>
+      <c r="V102" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
         </is>
       </c>
     </row>
@@ -8269,6 +8780,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="V103" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" s="2" t="n"/>
@@ -8344,6 +8860,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="V104" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" s="2" t="n"/>
@@ -8419,6 +8940,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="V105" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" s="2" t="n"/>
@@ -8494,6 +9020,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="V106" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" s="2" t="n"/>
@@ -8569,6 +9100,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="V107" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" s="2" t="n"/>
@@ -8646,6 +9182,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="V108" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" s="2" t="n"/>
@@ -8723,6 +9264,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="V109" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" s="2" t="n"/>
@@ -8798,6 +9344,11 @@
       <c r="U110" s="2" t="inlineStr">
         <is>
           <t>Соколова Анастасия Александровна</t>
+        </is>
+      </c>
+      <c r="V110" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
         </is>
       </c>
     </row>
@@ -8875,6 +9426,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="V111" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" s="2" t="n"/>
@@ -8950,6 +9506,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="V112" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" s="2" t="n"/>
@@ -9025,6 +9586,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="V113" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" s="2" t="n"/>
@@ -9100,6 +9666,11 @@
       <c r="U114" s="2" t="inlineStr">
         <is>
           <t>Абраамян Татьяна Викторовна</t>
+        </is>
+      </c>
+      <c r="V114" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
         </is>
       </c>
     </row>
@@ -9177,6 +9748,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="V115" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" s="2" t="n"/>
@@ -9252,6 +9828,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="V116" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" s="2" t="n"/>
@@ -9327,6 +9908,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="V117" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" s="2" t="n"/>
@@ -9402,6 +9988,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="V118" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" s="2" t="n"/>
@@ -9477,6 +10068,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="V119" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" s="2" t="n"/>
@@ -9552,6 +10148,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="V120" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" s="2" t="n"/>
@@ -9627,6 +10228,11 @@
       <c r="U121" s="2" t="inlineStr">
         <is>
           <t>Пеуна Анастасия Ивановна</t>
+        </is>
+      </c>
+      <c r="V121" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
         </is>
       </c>
     </row>
@@ -9704,6 +10310,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="V122" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" s="2" t="n"/>
@@ -9779,6 +10390,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="V123" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" s="2" t="n"/>
@@ -9854,6 +10470,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="V124" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" s="2" t="n"/>
@@ -9929,6 +10550,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="V125" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" s="2" t="n"/>
@@ -10004,6 +10630,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="V126" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" s="2" t="n"/>
@@ -10079,6 +10710,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="V127" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" s="2" t="n"/>
@@ -10154,6 +10790,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="V128" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" s="2" t="n"/>
@@ -10229,6 +10870,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="V129" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" s="2" t="n"/>
@@ -10304,6 +10950,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="V130" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" s="2" t="n"/>
@@ -10379,6 +11030,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="V131" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" s="2" t="n"/>
@@ -10454,6 +11110,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="V132" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" s="2" t="n"/>
@@ -10529,6 +11190,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="V133" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" s="2" t="n"/>
@@ -10604,6 +11270,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="V134" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" s="2" t="n"/>
@@ -10679,6 +11350,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="V135" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" s="2" t="n"/>
@@ -10754,6 +11430,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="V136" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" s="2" t="n"/>
@@ -10829,6 +11510,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="V137" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" s="2" t="n"/>
@@ -10904,6 +11590,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="V138" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" s="2" t="n"/>
@@ -10979,6 +11670,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="V139" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" s="2" t="n"/>
@@ -11054,6 +11750,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="V140" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" s="2" t="n"/>
@@ -11129,6 +11830,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="V141" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" s="2" t="n"/>
@@ -11204,6 +11910,11 @@
           <t>Васьковская Виктория Петровна</t>
         </is>
       </c>
+      <c r="V142" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" s="2" t="n"/>
@@ -11279,6 +11990,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="V143" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="144">
       <c r="A144" s="2" t="n"/>
@@ -11354,6 +12070,11 @@
           <t>Анухина Кристина Алексеевна</t>
         </is>
       </c>
+      <c r="V144" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="145">
       <c r="A145" s="2" t="n"/>
@@ -11429,6 +12150,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="V145" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="146">
       <c r="A146" s="2" t="n"/>
@@ -11504,6 +12230,11 @@
       <c r="U146" s="2" t="inlineStr">
         <is>
           <t>Пеуна Анастасия Ивановна</t>
+        </is>
+      </c>
+      <c r="V146" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
         </is>
       </c>
     </row>
@@ -11581,6 +12312,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="V147" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" s="2" t="n"/>
@@ -11656,6 +12392,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="V148" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="149">
       <c r="A149" s="2" t="n"/>
@@ -11731,6 +12472,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="V149" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="150">
       <c r="A150" s="2" t="n"/>
@@ -11806,6 +12552,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="V150" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="151">
       <c r="A151" s="2" t="n"/>
@@ -11881,6 +12632,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="V151" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="152">
       <c r="A152" s="2" t="n"/>
@@ -11956,6 +12712,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="V152" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="153">
       <c r="A153" s="2" t="n"/>
@@ -12031,6 +12792,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="V153" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" s="2" t="n"/>
@@ -12106,6 +12872,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="V154" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" s="2" t="n"/>
@@ -12181,6 +12952,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="V155" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="156">
       <c r="A156" s="2" t="n"/>
@@ -12256,6 +13032,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="V156" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" s="2" t="n"/>
@@ -12331,6 +13112,11 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="V157" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="158">
       <c r="A158" s="2" t="n"/>
@@ -12406,6 +13192,11 @@
           <t>Пеуна Анастасия Ивановна</t>
         </is>
       </c>
+      <c r="V158" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="159">
       <c r="A159" s="2" t="n"/>
@@ -12481,6 +13272,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="V159" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="160">
       <c r="A160" s="2" t="n"/>
@@ -12556,6 +13352,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="V160" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="161">
       <c r="A161" s="2" t="n"/>
@@ -12631,6 +13432,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="V161" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="162">
       <c r="A162" s="2" t="n"/>
@@ -12706,6 +13512,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="V162" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="163">
       <c r="A163" s="2" t="n"/>
@@ -12781,6 +13592,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="V163" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="164">
       <c r="A164" s="2" t="n"/>
@@ -12856,6 +13672,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="V164" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="165">
       <c r="A165" s="2" t="n"/>
@@ -12931,6 +13752,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="V165" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="166">
       <c r="A166" s="2" t="n"/>
@@ -13006,6 +13832,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="V166" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="167">
       <c r="A167" s="2" t="n"/>
@@ -13081,6 +13912,11 @@
           <t>Мартынова Дарья Дмитриевна</t>
         </is>
       </c>
+      <c r="V167" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="168">
       <c r="A168" s="2" t="n"/>
@@ -13156,6 +13992,11 @@
       <c r="U168" s="2" t="inlineStr">
         <is>
           <t>Абраамян Татьяна Викторовна</t>
+        </is>
+      </c>
+      <c r="V168" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
         </is>
       </c>
     </row>
@@ -13233,6 +14074,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="V169" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="170">
       <c r="A170" s="2" t="n"/>
@@ -13308,6 +14154,11 @@
           <t>Фёдорова Надежда Сергеевна</t>
         </is>
       </c>
+      <c r="V170" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Столица)</t>
+        </is>
+      </c>
     </row>
     <row r="171">
       <c r="A171" s="2" t="n"/>
@@ -13383,6 +14234,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="V171" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="172">
       <c r="A172" s="2" t="n"/>
@@ -13458,6 +14314,11 @@
           <t>Васильева Яна Денисовна</t>
         </is>
       </c>
+      <c r="V172" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="173">
       <c r="A173" s="2" t="n"/>
@@ -13533,6 +14394,11 @@
           <t>Абраамян Татьяна Викторовна</t>
         </is>
       </c>
+      <c r="V173" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="174">
       <c r="A174" s="2" t="n"/>
@@ -13608,6 +14474,11 @@
           <t>Пилия Анастасия Артуровна</t>
         </is>
       </c>
+      <c r="V174" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Гоголевский)</t>
+        </is>
+      </c>
     </row>
     <row r="175">
       <c r="A175" s="2" t="n"/>
@@ -13683,6 +14554,11 @@
           <t>Фёдорова Милана Андреевна</t>
         </is>
       </c>
+      <c r="V175" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="176">
       <c r="A176" s="2" t="n"/>
@@ -13758,6 +14634,11 @@
           <t>Лисовская Екатерина Александровна</t>
         </is>
       </c>
+      <c r="V176" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="177">
       <c r="A177" s="2" t="n"/>
@@ -13833,6 +14714,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="V177" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="178">
       <c r="A178" s="2" t="n"/>
@@ -13908,6 +14794,11 @@
           <t>Яковлева Александра Владимировна</t>
         </is>
       </c>
+      <c r="V178" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Промышленная)</t>
+        </is>
+      </c>
     </row>
     <row r="179">
       <c r="A179" s="2" t="n"/>
@@ -13983,6 +14874,11 @@
           <t>Соколова Анастасия Александровна</t>
         </is>
       </c>
+      <c r="V179" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
     <row r="180">
       <c r="A180" s="2" t="n"/>
@@ -14060,9 +14956,14 @@
           <t>Петрова Полина Владимировна</t>
         </is>
       </c>
+      <c r="V180" s="2" t="inlineStr">
+        <is>
+          <t>Фитнес Империя (Ровио)</t>
+        </is>
+      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:U180"/>
+  <autoFilter ref="A1:V180"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>